--- a/report/models/dev_v2_model_comparison.xlsx
+++ b/report/models/dev_v2_model_comparison.xlsx
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,13 +187,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -564,8 +565,8 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -591,12 +592,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>language</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mode</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -747,12 +748,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>no_term</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>ende</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>no_term</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -815,24 +816,20 @@
       <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>51.69980757375094</v>
+        <v>30.94776472211588</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>33.79461502418491</v>
+        <v>22.86721687236966</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>38.643176271946</v>
+        <v>24.68482631500832</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -840,13 +837,13 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>75.90388265109446</v>
+        <v>60.84477609028281</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>64.68123986854179</v>
+        <v>52.58790144965536</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>68.26380076747647</v>
+        <v>54.37295469501902</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -854,149 +851,121 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>84.90226337448561</v>
+        <v/>
       </c>
       <c r="L4" s="5" t="n">
-        <v>77.07047325102882</v>
+        <v/>
       </c>
       <c r="M4" s="5" t="n">
-        <v>80.3369341563786</v>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n">
-        <v>0.9539174811165551</v>
+        <v/>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.9439431090076802</v>
+        <v/>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>0.952332749063073</v>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n">
-        <v>0.8736383442265785</v>
+        <v/>
       </c>
       <c r="T4" s="5" t="n">
-        <v>0.8482207697893971</v>
+        <v/>
       </c>
       <c r="U4" s="5" t="n">
-        <v>0.87037037037037</v>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="V4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>47.40435687245185</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>29.55374793577898</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>34.42323375222445</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>72.13599682231188</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>59.89422664870388</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>63.92015107311587</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>86.86036426712923</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>72.96906620410523</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>79.89303266840128</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0.8993228848613932</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0.8845382532256466</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0.8929219390813675</v>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0.7864347826086984</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>0.7561739130434816</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>0.7718260869565234</v>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>50.16861638156919</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>40.9160373010399</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>44.66703003757013</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>70.44425755596352</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>65.10163897344826</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>67.43058465313958</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>enru</t>
+          <t>proper_term</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>30.94776472211588</v>
+        <v>51.69980757375094</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>22.86721687236966</v>
+        <v>33.79461502418491</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>24.68482631500832</v>
+        <v>38.643176271946</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1004,13 +973,13 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>60.84477609028281</v>
+        <v>75.90388265109446</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>52.58790144965536</v>
+        <v>64.68123986854179</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>54.37295469501902</v>
+        <v>68.26380076747647</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -1018,45 +987,53 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v/>
+        <v>84.90226337448561</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v/>
+        <v>77.07047325102882</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n"/>
+        <v>80.3369341563786</v>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="n">
-        <v/>
+        <v>0.9539174811165551</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v/>
+        <v>0.9439431090076802</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="5" t="n"/>
+        <v>0.952332749063073</v>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="n">
-        <v/>
+        <v>0.8736383442265785</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v/>
+        <v>0.8482207697893971</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="5" t="n"/>
+        <v>0.87037037037037</v>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>enru</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>proper_term</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -1131,106 +1108,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>enru</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>35.50499261674413</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>25.97487331721704</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>29.50320367768739</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>65.62814509898632</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>56.67427926456313</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>59.52284986795837</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>82.74456521739131</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>64.43614130434783</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>74.69429347826086</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0.8328214925865478</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0.8453649683301563</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0.834988152817287</v>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>60.60328379969123</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>49.93545671208923</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>54.69569022959442</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>78.55723644325373</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>72.17629913813785</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>75.16285839427655</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>96.76190476190477</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>90.53571428571429</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>93.23809523809523</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.9693862243160036</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>0.9602870569247431</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.9666112022279311</v>
       </c>
       <c r="R8" s="9" t="inlineStr">
         <is>
-          <t>Qwen 3B</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0.6508071367884458</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0.6737468139337289</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>0.6513735485698117</v>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0.885394070860448</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>0.8618944323933458</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>0.8778018799710753</v>
       </c>
       <c r="V8" s="9" t="inlineStr">
         <is>
-          <t>Qwen 3B</t>
+          <t>GPT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>enes</t>
+          <t>random_term</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>50.16861638156919</v>
+        <v>47.40435687245185</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>40.9160373010399</v>
+        <v>29.55374793577898</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>44.66703003757013</v>
+        <v>34.42323375222445</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -1238,13 +1211,13 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>70.44425755596352</v>
+        <v>72.13599682231188</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>65.10163897344826</v>
+        <v>59.89422664870388</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>67.43058465313958</v>
+        <v>63.92015107311587</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -1252,55 +1225,63 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v/>
+        <v>86.86036426712923</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v/>
+        <v>72.96906620410523</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n"/>
+        <v>79.89303266840128</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="n">
-        <v/>
+        <v>0.8993228848613932</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v/>
+        <v>0.8845382532256466</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="5" t="n"/>
+        <v>0.8929219390813675</v>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="S9" s="5" t="n">
-        <v/>
+        <v>0.7864347826086984</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v/>
+        <v>0.7561739130434816</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="5" t="n"/>
+        <v>0.7718260869565234</v>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>enes</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>60.60328379969123</v>
+        <v>35.50499261674413</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>49.93545671208923</v>
+        <v>25.97487331721704</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>54.69569022959442</v>
+        <v>29.50320367768739</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -1308,13 +1289,13 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>78.55723644325373</v>
+        <v>65.62814509898632</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>72.17629913813785</v>
+        <v>56.67427926456313</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>75.16285839427655</v>
+        <v>59.52284986795837</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -1322,13 +1303,13 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>96.76190476190477</v>
+        <v>82.74456521739131</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>90.53571428571429</v>
+        <v>64.43614130434783</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>93.23809523809523</v>
+        <v>74.69429347826086</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -1336,123 +1317,122 @@
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.9693862243160036</v>
+        <v>0.8328214925865478</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.9602870569247431</v>
+        <v>0.8453649683301563</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>0.9666112022279311</v>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
+        <v>0.834988152817287</v>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>Qwen 3B</t>
         </is>
       </c>
       <c r="S10" s="5" t="n">
-        <v>0.885394070860448</v>
+        <v>0.6508071367884458</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>0.8618944323933458</v>
+        <v>0.6737468139337289</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0.8778018799710753</v>
-      </c>
-      <c r="V10" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
+        <v>0.6513735485698117</v>
+      </c>
+      <c r="V10" s="10" t="inlineStr">
+        <is>
+          <t>Qwen 3B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>53.85311374110947</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>43.33054272486821</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>47.97280217248825</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>74.37205031940162</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>68.09978160962339</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>70.88348427463508</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>93.50850077279753</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="8" t="n">
         <v>84.23493044822257</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>88.75579598145286</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="n">
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>0.8905223371977781</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="8" t="n">
         <v>0.8879255899755327</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="8" t="n">
         <v>0.8882304176573891</v>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="n">
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="n">
         <v>0.7624209575429114</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="8" t="n">
         <v>0.7536886479975941</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="8" t="n">
         <v>0.7560975609756128</v>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>GPT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
